--- a/myProject/Assets/Config/Level.xlsx
+++ b/myProject/Assets/Config/Level.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>tag</t>
   </si>
@@ -38,6 +38,12 @@
   </si>
   <si>
     <t>content</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>number</t>
   </si>
   <si>
     <t>level_1</t>
@@ -48,38 +54,28 @@
   "faceMode": 1,
   "valueMin": 1,
   "valueMax": 12,
-  "randomSeed": 0,
+  "randomSeed": 1,
   "cards": [
-    {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a11"]},
     {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a5","layer":0,"logicRow":0,"logicCol":4,"useAbsolutePosition":false,"displayX":400,"displayY":0,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a6","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a7","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a3","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a4","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a12"]},
+    {"cardId":"a5","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a6","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a7","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a13"]},
     {"cardId":"a8","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a9","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a10","layer":0,"logicRow":1,"logicCol":4,"useAbsolutePosition":false,"displayX":400,"displayY":160,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a11","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a12","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a13","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a14","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a15","layer":0,"logicRow":2,"logicCol":4,"useAbsolutePosition":false,"displayX":400,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a16","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a17","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a18","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a19","layer":0,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a20","layer":0,"logicRow":3,"logicCol":4,"useAbsolutePosition":false,"displayX":400,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a21","layer":0,"logicRow":4,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":640,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a22","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a23","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a24","layer":0,"logicRow":4,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":640,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a25","layer":0,"logicRow":4,"logicCol":4,"useAbsolutePosition":false,"displayX":400,"displayY":640,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a26","layer":0,"logicRow":5,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":800,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a27","layer":0,"logicRow":5,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":800,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a28","layer":0,"logicRow":5,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":800,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a29","layer":0,"logicRow":5,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":800,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a30","layer":0,"logicRow":5,"logicCol":4,"useAbsolutePosition":false,"displayX":400,"displayY":800,"faceValue":0,"blockedByCardIds":[]}
+    {"cardId":"a9","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a10","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a11","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a12","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a13","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a14"]},
+    {"cardId":"a14","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a15","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a16","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a17","layer":1,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a18","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a19","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
+    {"cardId":"a20","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}
   ]
 }</t>
   </si>
@@ -87,28 +83,37 @@
     <t>level_2</t>
   </si>
   <si>
+    <t>{ "levelId": "L2", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 2, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a12"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a13"]}, {"cardId":"a4","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a7","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a10","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a12","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a14","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+  </si>
+  <si>
     <t>level_3</t>
   </si>
   <si>
+    <t>{ "levelId": "L3", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 3, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a13"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a4","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a7","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a10","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a12","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":1,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a15","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a18","layer":2,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+  </si>
+  <si>
     <t>level_4</t>
   </si>
   <si>
+    <t>{ "levelId": "L4", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 4, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a16","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a19","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+  </si>
+  <si>
     <t>level_5</t>
   </si>
   <si>
+    <t>{ "levelId": "L5", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 5, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a17","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a20","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+  </si>
+  <si>
     <t>level_6</t>
   </si>
   <si>
+    <t>{ "levelId": "L6", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 6, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a22"]}, {"cardId":"a21","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":0,"logicRow":4,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a29","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a30","layer":0,"logicRow":4,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+  </si>
+  <si>
     <t>level_7</t>
   </si>
   <si>
-    <t>level_8</t>
-  </si>
-  <si>
-    <t>level_9</t>
-  </si>
-  <si>
-    <t>level_10</t>
+    <t>{ "levelId": "L7", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 7, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":0,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a22"]}, {"cardId":"a19","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a23"]}, {"cardId":"a22","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a29","layer":0,"logicRow":4,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a30","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a31","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a32","layer":0,"logicRow":4,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
   </si>
 </sst>
 </file>
@@ -724,12 +729,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1042,7 +1050,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="51.7272727272727" customWidth="1"/>
@@ -1059,114 +1067,92 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="3" ht="409.5" spans="1:3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
         <v>4</v>
       </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" ht="409.5" spans="1:3">
-      <c r="A4" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5" ht="409.5" spans="1:3">
-      <c r="A5" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
         <v>7</v>
       </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" ht="409.5" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" ht="409.5" spans="1:3">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" ht="409.5" spans="1:3">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" ht="409.5" spans="1:3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" ht="409.5" spans="1:3">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" ht="409.5" spans="1:3">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>4</v>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/myProject/Assets/Config/Level.xlsx
+++ b/myProject/Assets/Config/Level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7630"/>
+    <workbookView windowWidth="16155" windowHeight="6945"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
   "levelId": "L1",
   "faceMode": 1,
   "valueMin": 1,
-  "valueMax": 12,
+  "valueMax": 12,"time":300,
   "randomSeed": 1,
   "cards": [
     {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a11"]},
@@ -83,37 +83,37 @@
     <t>level_2</t>
   </si>
   <si>
-    <t>{ "levelId": "L2", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 2, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a12"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a13"]}, {"cardId":"a4","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a7","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a10","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a12","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a14","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{ "levelId": "L2", "faceMode": 1,"time":300, "valueMin": 1, "valueMax": 12, "randomSeed": 2, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a12"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a13"]}, {"cardId":"a4","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a7","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a10","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a12","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a14","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]} ] }</t>
   </si>
   <si>
     <t>level_3</t>
   </si>
   <si>
-    <t>{ "levelId": "L3", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 3, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a13"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a4","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a7","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a10","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a12","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":1,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a15","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a18","layer":2,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{ "levelId": "L3", "faceMode": 1,"time":300, "valueMin": 1, "valueMax": 12, "randomSeed": 3, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a13"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a4","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a7","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a10","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a12","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":1,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a15","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a18","layer":2,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]} ] }</t>
   </si>
   <si>
     <t>level_4</t>
   </si>
   <si>
-    <t>{ "levelId": "L4", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 4, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a16","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a19","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{ "levelId": "L4", "faceMode": 1,"time":300, "valueMin": 1, "valueMax": 12, "randomSeed": 4, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a16","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a19","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]} ] }</t>
   </si>
   <si>
     <t>level_5</t>
   </si>
   <si>
-    <t>{ "levelId": "L5", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 5, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a17","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a20","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{ "levelId": "L5", "faceMode": 1,"time":300, "valueMin": 1, "valueMax": 12, "randomSeed": 5, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a17","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a20","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
   </si>
   <si>
     <t>level_6</t>
   </si>
   <si>
-    <t>{ "levelId": "L6", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 6, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a22"]}, {"cardId":"a21","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":0,"logicRow":4,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a29","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a30","layer":0,"logicRow":4,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{ "levelId": "L6", "faceMode": 1, "time":300,"valueMin": 1, "valueMax": 12, "randomSeed": 6, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a22"]}, {"cardId":"a21","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":0,"logicRow":4,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a29","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a30","layer":0,"logicRow":4,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
   </si>
   <si>
     <t>level_7</t>
   </si>
   <si>
-    <t>{ "levelId": "L7", "faceMode": 1, "valueMin": 1, "valueMax": 12, "randomSeed": 7, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":0,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a22"]}, {"cardId":"a19","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a23"]}, {"cardId":"a22","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a29","layer":0,"logicRow":4,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a30","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a31","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a32","layer":0,"logicRow":4,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{ "levelId": "L7", "faceMode": 1,"time":300, "valueMin": 1, "valueMax": 12, "randomSeed": 7, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":0,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a22"]}, {"cardId":"a19","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a23"]}, {"cardId":"a22","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a29","layer":0,"logicRow":4,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a30","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a31","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a32","layer":0,"logicRow":4,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
   </si>
 </sst>
 </file>
@@ -1078,14 +1078,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" ht="409.5" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/myProject/Assets/Config/Level.xlsx
+++ b/myProject/Assets/Config/Level.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16155" windowHeight="6945"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="16155" windowHeight="6945" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29">
   <si>
     <t>tag</t>
   </si>
@@ -53,29 +40,245 @@
   "levelId": "L1",
   "faceMode": 1,
   "valueMin": 1,
-  "valueMax": 12,"time":300,
+  "valueMax": 12,
+  "time": 210,
+  "queueMaxSlots": 5,
+  "queueMax": 5,
   "randomSeed": 1,
   "cards": [
-    {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a11"]},
-    {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a3","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a4","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a12"]},
-    {"cardId":"a5","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a6","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a7","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a13"]},
-    {"cardId":"a8","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a9","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a10","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a11","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a12","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a13","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a14"]},
-    {"cardId":"a14","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a15","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a16","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a17","layer":1,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a18","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a19","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]},
-    {"cardId":"a20","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a13",
+        "a19"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a18"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a16"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a15"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a13",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a19"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a20"
+      ]
+    },
+    {
+      "cardId": "a15",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a16",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a17",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a18",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a19",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a20",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
   ]
 }</t>
   </si>
@@ -83,205 +286,4558 @@
     <t>level_2</t>
   </si>
   <si>
-    <t>{ "levelId": "L2", "faceMode": 1,"time":300, "valueMin": 1, "valueMax": 12, "randomSeed": 2, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a12"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a13"]}, {"cardId":"a4","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a7","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a10","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a12","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a14","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{
+  "levelId": "L2",
+  "faceMode": 1,
+  "valueMin": 1,
+  "valueMax": 12,
+  "time": 220,
+  "queueMaxSlots": 5,
+  "queueMax": 5,
+  "randomSeed": 2,
+  "cards": [
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a13",
+        "a21"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a18"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a16"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a15"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a19"
+      ]
+    },
+    {
+      "cardId": "a13",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a21"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a22"
+      ]
+    },
+    {
+      "cardId": "a15",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a16",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a17",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a18",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a19",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a20",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a21",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a22",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
+  ]
+}</t>
   </si>
   <si>
     <t>level_3</t>
   </si>
   <si>
-    <t>{ "levelId": "L3", "faceMode": 1,"time":300, "valueMin": 1, "valueMax": 12, "randomSeed": 3, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a13"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a4","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a7","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a10","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a12","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":1,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a15","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a18","layer":2,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{
+  "levelId": "L3",
+  "faceMode": 1,
+  "valueMin": 1,
+  "valueMax": 12,
+  "time": 230,
+  "queueMaxSlots": 5,
+  "queueMax": 5,
+  "randomSeed": 3,
+  "cards": [
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a15",
+        "a23"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a20"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a18"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a17"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a21"
+      ]
+    },
+    {
+      "cardId": "a13",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a19"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a15",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a23"
+      ]
+    },
+    {
+      "cardId": "a16",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a24"
+      ]
+    },
+    {
+      "cardId": "a17",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a18",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a19",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a20",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a21",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a22",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a23",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a24",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
+  ]
+}</t>
   </si>
   <si>
     <t>level_4</t>
   </si>
   <si>
-    <t>{ "levelId": "L4", "faceMode": 1,"time":300, "valueMin": 1, "valueMax": 12, "randomSeed": 4, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a14"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a16","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a19","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{
+  "levelId": "L4",
+  "faceMode": 1,
+  "valueMin": 1,
+  "valueMax": 12,
+  "time": 240,
+  "queueMaxSlots": 6,
+  "queueMax": 6,
+  "randomSeed": 4,
+  "cards": [
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a15",
+        "a23"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a20"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a18"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a17"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a21"
+      ]
+    },
+    {
+      "cardId": "a13",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a19"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a25"
+      ]
+    },
+    {
+      "cardId": "a15",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a23"
+      ]
+    },
+    {
+      "cardId": "a16",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a24"
+      ]
+    },
+    {
+      "cardId": "a17",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a18",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a19",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a20",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a21",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a22",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a23",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a24",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a25",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a26",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
+  ]
+}</t>
   </si>
   <si>
     <t>level_5</t>
   </si>
   <si>
-    <t>{ "levelId": "L5", "faceMode": 1,"time":300, "valueMin": 1, "valueMax": 12, "randomSeed": 5, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a15"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a17","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a20","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":1,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{
+  "levelId": "L5",
+  "faceMode": 1,
+  "valueMin": 1,
+  "valueMax": 12,
+  "time": 255,
+  "queueMaxSlots": 6,
+  "queueMax": 6,
+  "randomSeed": 5,
+  "cards": [
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a17",
+        "a25"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a22"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a20"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a19"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a23"
+      ]
+    },
+    {
+      "cardId": "a13",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a21"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a27"
+      ]
+    },
+    {
+      "cardId": "a15",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a16",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a17",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a25"
+      ]
+    },
+    {
+      "cardId": "a18",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a26"
+      ]
+    },
+    {
+      "cardId": "a19",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a20",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a21",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a22",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a23",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a24",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a25",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a26",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a27",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a28",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
+  ]
+}</t>
   </si>
   <si>
     <t>level_6</t>
   </si>
   <si>
-    <t>{ "levelId": "L6", "faceMode": 1, "time":300,"valueMin": 1, "valueMax": 12, "randomSeed": 6, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a16"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a18","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a19","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a22"]}, {"cardId":"a21","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a22","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":1,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":0,"logicRow":4,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a29","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a30","layer":0,"logicRow":4,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{
+  "levelId": "L6",
+  "faceMode": 1,
+  "valueMin": 1,
+  "valueMax": 12,
+  "time": 270,
+  "queueMaxSlots": 6,
+  "queueMax": 6,
+  "randomSeed": 6,
+  "cards": [
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a17",
+        "a27"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a22"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a20"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a19"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a23"
+      ]
+    },
+    {
+      "cardId": "a13",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a21"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a25",
+        "a29"
+      ]
+    },
+    {
+      "cardId": "a15",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a16",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a17",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a27"
+      ]
+    },
+    {
+      "cardId": "a18",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a28"
+      ]
+    },
+    {
+      "cardId": "a19",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a20",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a21",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a22",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a23",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a24",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a25",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a29"
+      ]
+    },
+    {
+      "cardId": "a26",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a30"
+      ]
+    },
+    {
+      "cardId": "a27",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a28",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a29",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a30",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
+  ]
+}</t>
   </si>
   <si>
     <t>level_7</t>
   </si>
   <si>
-    <t>{ "levelId": "L7", "faceMode": 1,"time":300, "valueMin": 1, "valueMax": 12, "randomSeed": 7, "cards": [ {"cardId":"a1","layer":0,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":["a17"]}, {"cardId":"a2","layer":0,"logicRow":0,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a3","layer":0,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a18"]}, {"cardId":"a4","layer":0,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a5","layer":0,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a6","layer":0,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":["a19"]}, {"cardId":"a7","layer":0,"logicRow":1,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a8","layer":0,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":["a20"]}, {"cardId":"a9","layer":0,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a10","layer":0,"logicRow":2,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a11","layer":0,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a21"]}, {"cardId":"a12","layer":0,"logicRow":2,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a13","layer":0,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a14","layer":0,"logicRow":3,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a15","layer":0,"logicRow":3,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a16","layer":0,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a17","layer":1,"logicRow":0,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a18","layer":1,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":["a22"]}, {"cardId":"a19","layer":1,"logicRow":1,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a20","layer":1,"logicRow":1,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a21","layer":1,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":["a23"]}, {"cardId":"a22","layer":2,"logicRow":0,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a23","layer":2,"logicRow":2,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a24","layer":1,"logicRow":3,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a25","layer":1,"logicRow":3,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":480,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a26","layer":1,"logicRow":1,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":160,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a27","layer":1,"logicRow":2,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":320,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a28","layer":1,"logicRow":0,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":0,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a29","layer":0,"logicRow":4,"logicCol":0,"useAbsolutePosition":false,"displayX":0,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a30","layer":0,"logicRow":4,"logicCol":1,"useAbsolutePosition":false,"displayX":100,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a31","layer":0,"logicRow":4,"logicCol":2,"useAbsolutePosition":false,"displayX":200,"displayY":640,"faceValue":0,"blockedByCardIds":[]}, {"cardId":"a32","layer":0,"logicRow":4,"logicCol":3,"useAbsolutePosition":false,"displayX":300,"displayY":640,"faceValue":0,"blockedByCardIds":[]} ] }</t>
+    <t>{
+  "levelId": "L7",
+  "faceMode": 1,
+  "valueMin": 1,
+  "valueMax": 12,
+  "time": 285,
+  "queueMaxSlots": 7,
+  "queueMax": 7,
+  "randomSeed": 7,
+  "cards": [
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a19",
+        "a29"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a24"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a22"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a21"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a25"
+      ]
+    },
+    {
+      "cardId": "a13",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a23"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a27",
+        "a31"
+      ]
+    },
+    {
+      "cardId": "a15",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a16",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a17",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a28",
+        "a32"
+      ]
+    },
+    {
+      "cardId": "a18",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a20",
+        "a30"
+      ]
+    },
+    {
+      "cardId": "a19",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a29"
+      ]
+    },
+    {
+      "cardId": "a20",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a30"
+      ]
+    },
+    {
+      "cardId": "a21",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a22",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a23",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a24",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a25",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a26",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a27",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a31"
+      ]
+    },
+    {
+      "cardId": "a28",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a32"
+      ]
+    },
+    {
+      "cardId": "a29",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a30",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a31",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a32",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>level_8</t>
+  </si>
+  <si>
+    <t>{
+  "levelId": "L8",
+  "faceMode": 1,
+  "valueMin": 1,
+  "valueMax": 12,
+  "time": 300,
+  "queueMaxSlots": 7,
+  "queueMax": 7,
+  "randomSeed": 8,
+  "cards": [
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a19",
+        "a29"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a24"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a22"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a21"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a25"
+      ]
+    },
+    {
+      "cardId": "a13",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a23"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a27",
+        "a31"
+      ]
+    },
+    {
+      "cardId": "a15",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a16",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a17",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a28",
+        "a32",
+        "a33"
+      ]
+    },
+    {
+      "cardId": "a18",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a20",
+        "a30",
+        "a34"
+      ]
+    },
+    {
+      "cardId": "a19",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a29"
+      ]
+    },
+    {
+      "cardId": "a20",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a30",
+        "a34"
+      ]
+    },
+    {
+      "cardId": "a21",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a22",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a23",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a24",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a25",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a26",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a27",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a31"
+      ]
+    },
+    {
+      "cardId": "a28",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a32",
+        "a33"
+      ]
+    },
+    {
+      "cardId": "a29",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a30",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a34"
+      ]
+    },
+    {
+      "cardId": "a31",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a32",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a33"
+      ]
+    },
+    {
+      "cardId": "a33",
+      "layer": 3,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a34",
+      "layer": 3,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>level_9</t>
+  </si>
+  <si>
+    <t>{
+  "levelId": "L9",
+  "faceMode": 1,
+  "valueMin": 1,
+  "valueMax": 12,
+  "time": 315,
+  "queueMaxSlots": 7,
+  "queueMax": 7,
+  "randomSeed": 9,
+  "cards": [
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a21",
+        "a31"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a26"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a24"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a23"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a27"
+      ]
+    },
+    {
+      "cardId": "a13",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a25"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a29",
+        "a33"
+      ]
+    },
+    {
+      "cardId": "a15",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a16",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a17",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a30",
+        "a34",
+        "a35"
+      ]
+    },
+    {
+      "cardId": "a18",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a22",
+        "a32",
+        "a36"
+      ]
+    },
+    {
+      "cardId": "a19",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a20",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a21",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a31"
+      ]
+    },
+    {
+      "cardId": "a22",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a32",
+        "a36"
+      ]
+    },
+    {
+      "cardId": "a23",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a24",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a25",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a26",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a27",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a28",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a29",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a33"
+      ]
+    },
+    {
+      "cardId": "a30",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a34",
+        "a35"
+      ]
+    },
+    {
+      "cardId": "a31",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a32",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a36"
+      ]
+    },
+    {
+      "cardId": "a33",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a34",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a35"
+      ]
+    },
+    {
+      "cardId": "a35",
+      "layer": 3,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a36",
+      "layer": 3,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>level_10</t>
+  </si>
+  <si>
+    <t>{
+  "levelId": "L10",
+  "faceMode": 1,
+  "valueMin": 1,
+  "valueMax": 12,
+  "time": 330,
+  "queueMaxSlots": 8,
+  "queueMax": 8,
+  "randomSeed": 10,
+  "cards": [
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a21",
+        "a33"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a32"
+      ]
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a26"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a24"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a23"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a27"
+      ]
+    },
+    {
+      "cardId": "a13",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a25"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a29",
+        "a35"
+      ]
+    },
+    {
+      "cardId": "a15",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a31"
+      ]
+    },
+    {
+      "cardId": "a16",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a17",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a30",
+        "a36",
+        "a37"
+      ]
+    },
+    {
+      "cardId": "a18",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a22",
+        "a34",
+        "a38"
+      ]
+    },
+    {
+      "cardId": "a19",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a20",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a21",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a33"
+      ]
+    },
+    {
+      "cardId": "a22",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a34",
+        "a38"
+      ]
+    },
+    {
+      "cardId": "a23",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a24",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a25",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a26",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a27",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a28",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a29",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a35"
+      ]
+    },
+    {
+      "cardId": "a30",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a36",
+        "a37"
+      ]
+    },
+    {
+      "cardId": "a31",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a32",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a33",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a34",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a38"
+      ]
+    },
+    {
+      "cardId": "a35",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a36",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a37"
+      ]
+    },
+    {
+      "cardId": "a37",
+      "layer": 3,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a38",
+      "layer": 3,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>level_11</t>
+  </si>
+  <si>
+    <t>{
+  "levelId": "L11",
+  "faceMode": 1,
+  "valueMin": 1,
+  "valueMax": 12,
+  "time": 345,
+  "queueMaxSlots": 8,
+  "queueMax": 8,
+  "randomSeed": 11,
+  "cards": [
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a23",
+        "a35"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a34"
+      ]
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a28"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a26"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a25"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a29"
+      ]
+    },
+    {
+      "cardId": "a13",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a27"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a31",
+        "a37"
+      ]
+    },
+    {
+      "cardId": "a15",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a33"
+      ]
+    },
+    {
+      "cardId": "a16",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a17",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a32",
+        "a38",
+        "a39"
+      ]
+    },
+    {
+      "cardId": "a18",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a24",
+        "a36",
+        "a40"
+      ]
+    },
+    {
+      "cardId": "a19",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a20",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a21",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a30"
+      ]
+    },
+    {
+      "cardId": "a22",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a23",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a35"
+      ]
+    },
+    {
+      "cardId": "a24",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a36",
+        "a40"
+      ]
+    },
+    {
+      "cardId": "a25",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a26",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a27",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a28",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a29",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a30",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a31",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a37"
+      ]
+    },
+    {
+      "cardId": "a32",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a38",
+        "a39"
+      ]
+    },
+    {
+      "cardId": "a33",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a34",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a35",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a36",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a40"
+      ]
+    },
+    {
+      "cardId": "a37",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a38",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a39"
+      ]
+    },
+    {
+      "cardId": "a39",
+      "layer": 3,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a40",
+      "layer": 3,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>level_12</t>
+  </si>
+  <si>
+    <t>{
+  "levelId": "L12",
+  "faceMode": 1,
+  "valueMin": 1,
+  "valueMax": 12,
+  "time": 360,
+  "queueMaxSlots": 8,
+  "queueMax": 8,
+  "randomSeed": 12,
+  "cards": [
+    {
+      "cardId": "a1",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a2",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a3",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a4",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a25",
+        "a37"
+      ]
+    },
+    {
+      "cardId": "a5",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a6",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a36"
+      ]
+    },
+    {
+      "cardId": "a7",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a30"
+      ]
+    },
+    {
+      "cardId": "a8",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a9",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a28"
+      ]
+    },
+    {
+      "cardId": "a10",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a11",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a27"
+      ]
+    },
+    {
+      "cardId": "a12",
+      "layer": 0,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a31"
+      ]
+    },
+    {
+      "cardId": "a13",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a29"
+      ]
+    },
+    {
+      "cardId": "a14",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a33",
+        "a39"
+      ]
+    },
+    {
+      "cardId": "a15",
+      "layer": 0,
+      "logicRow": 1,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a35"
+      ]
+    },
+    {
+      "cardId": "a16",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 0,
+      "useAbsolutePosition": false,
+      "displayX": 0,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a17",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a34",
+        "a40",
+        "a41"
+      ]
+    },
+    {
+      "cardId": "a18",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a26",
+        "a38",
+        "a42"
+      ]
+    },
+    {
+      "cardId": "a19",
+      "layer": 0,
+      "logicRow": 2,
+      "logicCol": 5,
+      "useAbsolutePosition": false,
+      "displayX": 500,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a20",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a21",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a32"
+      ]
+    },
+    {
+      "cardId": "a22",
+      "layer": 0,
+      "logicRow": 3,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a23",
+      "layer": 0,
+      "logicRow": 4,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 640,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a24",
+      "layer": 0,
+      "logicRow": 4,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 640,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a25",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a37"
+      ]
+    },
+    {
+      "cardId": "a26",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a38",
+        "a42"
+      ]
+    },
+    {
+      "cardId": "a27",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a28",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a29",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a30",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a31",
+      "layer": 1,
+      "logicRow": 0,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 0,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a32",
+      "layer": 1,
+      "logicRow": 3,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 480,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a33",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a39"
+      ]
+    },
+    {
+      "cardId": "a34",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a40",
+        "a41"
+      ]
+    },
+    {
+      "cardId": "a35",
+      "layer": 1,
+      "logicRow": 1,
+      "logicCol": 4,
+      "useAbsolutePosition": false,
+      "displayX": 400,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a36",
+      "layer": 1,
+      "logicRow": 2,
+      "logicCol": 1,
+      "useAbsolutePosition": false,
+      "displayX": 100,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a37",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a38",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a42"
+      ]
+    },
+    {
+      "cardId": "a39",
+      "layer": 2,
+      "logicRow": 1,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 160,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a40",
+      "layer": 2,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": [
+        "a41"
+      ]
+    },
+    {
+      "cardId": "a41",
+      "layer": 3,
+      "logicRow": 2,
+      "logicCol": 2,
+      "useAbsolutePosition": false,
+      "displayX": 200,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    },
+    {
+      "cardId": "a42",
+      "layer": 3,
+      "logicRow": 2,
+      "logicCol": 3,
+      "useAbsolutePosition": false,
+      "displayX": 300,
+      "displayY": 320,
+      "faceValue": 0,
+      "blockedByCardIds": []
+    }
+  ]
+}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -581,164 +5137,165 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -792,11 +5349,6 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1048,12 +5600,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
-    <col min="3" max="3" width="51.7272727272727" customWidth="1"/>
+    <col width="51.7272727272727" customWidth="1" style="3" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1078,11 +5633,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="409.5" spans="1:3">
+    <row r="3" spans="1:3" ht="409.5" customHeight="1" s="3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1093,7 +5648,7 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1104,7 +5659,7 @@
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1115,7 +5670,7 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1126,7 +5681,7 @@
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1137,7 +5692,7 @@
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1148,40 +5703,98 @@
       <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>